--- a/output/pdf_financials_xlsx/CTEK.xlsx
+++ b/output/pdf_financials_xlsx/CTEK.xlsx
@@ -1121,16 +1121,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.026713</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.034403</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.034403</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -2213,16 +2213,16 @@
         <v>-3.313889</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.185377</v>
+        <v>-4.21209</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.593429</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.685736</v>
+        <v>-1.720139</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.685736</v>
+        <v>-1.720139</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2349,16 +2349,16 @@
         <v>-3.221994</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.018924</v>
+        <v>-4.045637</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.426976</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.546012</v>
+        <v>-1.580415</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.544948</v>
+        <v>-1.579351</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2417,16 +2417,16 @@
         <v>-414.6160804938342</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1529.061467987643</v>
+        <v>-1539.224839824073</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-838.1918086403339</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-914.3184949937607</v>
+        <v>-934.6645849227331</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-699.5938143863066</v>
+        <v>-715.1724137931035</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.053542</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.179375</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.074337</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.225862</v>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.002918</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.775675</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.729124</v>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.053542</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.179375</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.074337</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.225862</v>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.002918</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.775675</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.729124</v>
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.396288</v>
+        <v>0.342746</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.319571</v>
+        <v>0.140196</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.173132</v>
+        <v>0.09879499999999999</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.069661</v>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.060663</v>
+        <v>0.057745</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.873345</v>
+        <v>0.09767000000000001</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.048154</v>
@@ -8234,13 +8234,13 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.042584</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.056116</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.062413</v>
       </c>
       <c r="J124" s="1" t="inlineStr">
         <is>
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.071544</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.01792</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -8296,13 +8296,13 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.042584</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.056116</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.062413</v>
       </c>
       <c r="J125" s="1" t="inlineStr">
         <is>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.071544</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.01792</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -35951,7 +35951,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
@@ -49345,7 +49345,11 @@
           <t>Finance lease payments (note 10)</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -50905,7 +50909,11 @@
           <t>Finance lease payments (note 10)</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -66117,7 +66125,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -68329,7 +68337,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -70026,7 +70034,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">

--- a/output/pdf_financials_xlsx/CTEK.xlsx
+++ b/output/pdf_financials_xlsx/CTEK.xlsx
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.023741</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.023741</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.023741</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0.091895</v>
@@ -41537,7 +41537,11 @@
           <t>Additions to intangible assets 6</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -44363,7 +44367,11 @@
           <t>Additions to intangible assets 6</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -47175,7 +47183,11 @@
           <t>Additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -54943,7 +54955,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E460" s="5" t="n">
@@ -76228,7 +76240,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E673" s="5" t="n">
